--- a/Data/EC/NIT-9008297144.xlsx
+++ b/Data/EC/NIT-9008297144.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED7CF2E6-4520-4888-8A49-0A068BED252E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{502035D1-E8A0-4D1A-B2D7-3CAA14FF4C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{D8236417-73B7-44CA-AADC-0774F259EE52}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{45390B90-2CD9-4FB6-9F86-54D47EB70F2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -524,22 +524,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{077E26FE-E84F-FFB3-E868-71FB41003ACC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D049391A-7F62-6BDC-DCB4-79336F55FC7D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -548,7 +548,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -561,7 +561,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -890,23 +890,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CC0A6C-10BF-4FCB-973F-18175872086A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AACC79BC-7B91-4634-AB7F-1890D2154040}">
   <dimension ref="B2:J63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -919,7 +919,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -930,7 +930,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -941,7 +941,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -952,8 +952,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>30</v>
       </c>
@@ -968,8 +968,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -984,8 +984,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>31</v>
       </c>
@@ -1000,8 +1000,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>32</v>
       </c>
@@ -1020,7 +1020,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1072,7 +1072,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1095,7 +1095,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1118,7 +1118,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1141,7 +1141,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1164,7 +1164,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1187,7 +1187,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1210,7 +1210,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1233,7 +1233,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1256,7 +1256,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1279,7 +1279,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1302,7 +1302,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1325,7 +1325,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1348,7 +1348,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1371,7 +1371,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1394,7 +1394,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1417,7 +1417,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1440,7 +1440,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1463,7 +1463,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1486,7 +1486,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1509,7 +1509,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1532,7 +1532,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1555,7 +1555,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1578,7 +1578,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1601,7 +1601,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1624,7 +1624,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1647,7 +1647,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1670,7 +1670,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1693,7 +1693,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1716,7 +1716,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1739,7 +1739,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1762,7 +1762,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1785,7 +1785,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1808,7 +1808,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1831,7 +1831,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1854,7 +1854,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -1877,7 +1877,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -1900,7 +1900,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -1923,7 +1923,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -1946,7 +1946,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -1969,7 +1969,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -1992,7 +1992,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="21" t="s">
         <v>8</v>
       </c>
@@ -2015,7 +2015,7 @@
       <c r="I57" s="25"/>
       <c r="J57" s="26"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="32" t="s">
         <v>38</v>
       </c>
@@ -2026,7 +2026,7 @@
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="32" t="s">
         <v>37</v>
       </c>
